--- a/outputs/statistics_output.xlsx
+++ b/outputs/statistics_output.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Documents\School\THESIS\Publications\Third Submission\New Analysis\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178ADDA2-4588-4B67-B23A-DF434D300791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD680356-8208-4F73-A5FE-EAA2CE478CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="demographics" sheetId="1" r:id="rId1"/>
-    <sheet name="rotation_data_by_arm" sheetId="2" r:id="rId2"/>
-    <sheet name="rotation_rate_distribution" sheetId="3" r:id="rId3"/>
-    <sheet name="cumulative_rotation_stats" sheetId="4" r:id="rId4"/>
-    <sheet name="rotation_rate_stats" sheetId="5" r:id="rId5"/>
-    <sheet name="difference_model_stats" sheetId="6" r:id="rId6"/>
+    <sheet name="raw_demographics" sheetId="1" r:id="rId1"/>
+    <sheet name="demographics_summary" sheetId="2" r:id="rId2"/>
+    <sheet name="rotation_data_by_arm" sheetId="3" r:id="rId3"/>
+    <sheet name="rotation_rate_distribution" sheetId="4" r:id="rId4"/>
+    <sheet name="cumulative_rotation_stats" sheetId="5" r:id="rId5"/>
+    <sheet name="rotation_rate_stats" sheetId="6" r:id="rId6"/>
+    <sheet name="difference_model_stats" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="177">
   <si>
     <t>participant</t>
   </si>
@@ -180,6 +181,195 @@
     <t>10:17:32</t>
   </si>
   <si>
+    <t>Characteristic</t>
+  </si>
+  <si>
+    <t>Statistic</t>
+  </si>
+  <si>
+    <t>Female (n = 11)</t>
+  </si>
+  <si>
+    <t>Male (n = 8)</t>
+  </si>
+  <si>
+    <t>All (n = 19)</t>
+  </si>
+  <si>
+    <t>Age (years)</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Mean ± SD</t>
+  </si>
+  <si>
+    <t>75.8 ± 8.4</t>
+  </si>
+  <si>
+    <t>73.6 ± 4.7</t>
+  </si>
+  <si>
+    <t>74.9 ± 7.0</t>
+  </si>
+  <si>
+    <t>Median [IQR]</t>
+  </si>
+  <si>
+    <t>78.0 [77.5–80.0]</t>
+  </si>
+  <si>
+    <t>73.5 [70.5–76.5]</t>
+  </si>
+  <si>
+    <t>78.0 [71.5–79.5]</t>
+  </si>
+  <si>
+    <t>Range (min–max)</t>
+  </si>
+  <si>
+    <t>56.0–84.0</t>
+  </si>
+  <si>
+    <t>67.0–81.0</t>
+  </si>
+  <si>
+    <t>Skewness</t>
+  </si>
+  <si>
+    <t>-1.57</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>-1.24</t>
+  </si>
+  <si>
+    <t>Recording start time (hh:mm)</t>
+  </si>
+  <si>
+    <t>10:08 ± 66 min</t>
+  </si>
+  <si>
+    <t>09:02 ± 43 min</t>
+  </si>
+  <si>
+    <t>09:40 ± 65 min</t>
+  </si>
+  <si>
+    <t>10:05 [09:27–10:34]</t>
+  </si>
+  <si>
+    <t>08:47 [08:38–09:12]</t>
+  </si>
+  <si>
+    <t>09:22 [08:47–10:13]</t>
+  </si>
+  <si>
+    <t>08:33–12:16</t>
+  </si>
+  <si>
+    <t>08:19–10:37</t>
+  </si>
+  <si>
+    <t>08:19–12:16</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>1.42</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>Recording duration (hours)</t>
+  </si>
+  <si>
+    <t>10.0 ± 2.6</t>
+  </si>
+  <si>
+    <t>11.2 ± 3.6</t>
+  </si>
+  <si>
+    <t>10.5 ± 3.0</t>
+  </si>
+  <si>
+    <t>10.8 [7.6–12.0]</t>
+  </si>
+  <si>
+    <t>12.5 [9.2–13.2]</t>
+  </si>
+  <si>
+    <t>11.2 [8.1–12.8]</t>
+  </si>
+  <si>
+    <t>6.5–14.0</t>
+  </si>
+  <si>
+    <t>4.5–15.2</t>
+  </si>
+  <si>
+    <t>-0.05</t>
+  </si>
+  <si>
+    <t>-0.81</t>
+  </si>
+  <si>
+    <t>-0.34</t>
+  </si>
+  <si>
+    <t>RTSA side, n (%)</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>4 (36%)</t>
+  </si>
+  <si>
+    <t>2 (25%)</t>
+  </si>
+  <si>
+    <t>6 (32%)</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>7 (64%)</t>
+  </si>
+  <si>
+    <t>6 (75%)</t>
+  </si>
+  <si>
+    <t>13 (68%)</t>
+  </si>
+  <si>
+    <t>RTSA on dominant arm, n (%)</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>9 (82%)</t>
+  </si>
+  <si>
+    <t>15 (79%)</t>
+  </si>
+  <si>
     <t>Operated cumulative rotation</t>
   </si>
   <si>
@@ -198,9 +388,6 @@
     <t>Measure</t>
   </si>
   <si>
-    <t>n</t>
-  </si>
-  <si>
     <t>Mean</t>
   </si>
   <si>
@@ -226,9 +413,6 @@
   </si>
   <si>
     <t>Max</t>
-  </si>
-  <si>
-    <t>Skewness</t>
   </si>
   <si>
     <t>Shapiro-Wilk p</t>
@@ -714,17 +898,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1313,476 +1486,296 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>0</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2">
-        <v>868008.31831978529</v>
-      </c>
-      <c r="D2">
-        <v>1000814.759840359</v>
-      </c>
-      <c r="E2">
-        <v>77172.872838146141</v>
-      </c>
-      <c r="F2">
-        <v>88980.426299607323</v>
-      </c>
-      <c r="G2">
-        <v>11.247583333333329</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>1111428.2606788049</v>
-      </c>
-      <c r="D3">
-        <v>1117221.440602904</v>
-      </c>
-      <c r="E3">
-        <v>87183.190178210367</v>
-      </c>
-      <c r="F3">
-        <v>87637.621584112261</v>
-      </c>
-      <c r="G3">
-        <v>12.74819444444444</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4">
-        <v>422304.31443212618</v>
-      </c>
-      <c r="D4">
-        <v>524531.94911013381</v>
-      </c>
-      <c r="E4">
-        <v>65044.389812077687</v>
-      </c>
-      <c r="F4">
-        <v>80789.751373217267</v>
-      </c>
-      <c r="G4">
-        <v>6.4925555555555556</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5">
-        <v>444382.76247065351</v>
-      </c>
-      <c r="D5">
-        <v>344184.86684617552</v>
-      </c>
-      <c r="E5">
-        <v>54346.006029655036</v>
-      </c>
-      <c r="F5">
-        <v>42092.255660284602</v>
-      </c>
-      <c r="G5">
-        <v>8.1769166666666671</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>4</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6">
-        <v>1520524.386244345</v>
-      </c>
-      <c r="D6">
-        <v>1568390.7439207369</v>
-      </c>
-      <c r="E6">
-        <v>108652.64760369041</v>
-      </c>
-      <c r="F6">
-        <v>112073.0508144085</v>
-      </c>
-      <c r="G6">
-        <v>13.994361111111109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5</v>
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7">
-        <v>533413.82988175692</v>
-      </c>
-      <c r="D7">
-        <v>447628.65891148383</v>
-      </c>
-      <c r="E7">
-        <v>43545.763490898164</v>
-      </c>
-      <c r="F7">
-        <v>36542.6065481435</v>
-      </c>
-      <c r="G7">
-        <v>12.249499999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>6</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8">
-        <v>582664.38348372676</v>
-      </c>
-      <c r="D8">
-        <v>933730.03242899757</v>
-      </c>
-      <c r="E8">
-        <v>48577.067545023972</v>
-      </c>
-      <c r="F8">
-        <v>77845.61428472423</v>
-      </c>
-      <c r="G8">
-        <v>11.99463888888889</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>7</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="C8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9">
-        <v>797053.15886286262</v>
-      </c>
-      <c r="D9">
-        <v>749001.71142912155</v>
-      </c>
-      <c r="E9">
-        <v>56938.130086701327</v>
-      </c>
-      <c r="F9">
-        <v>53505.536495654072</v>
-      </c>
-      <c r="G9">
-        <v>13.998583333333331</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>8</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10">
-        <v>602680.2409760782</v>
-      </c>
-      <c r="D10">
-        <v>566191.97830694204</v>
-      </c>
-      <c r="E10">
-        <v>135224.42582730119</v>
-      </c>
-      <c r="F10">
-        <v>127037.4901466513</v>
-      </c>
-      <c r="G10">
-        <v>4.4568888888888889</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>9</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11">
-        <v>1148570.4072544051</v>
-      </c>
-      <c r="D11">
-        <v>1111210.7757937161</v>
-      </c>
-      <c r="E11">
-        <v>89426.406404235895</v>
-      </c>
-      <c r="F11">
-        <v>86517.627312406097</v>
-      </c>
-      <c r="G11">
-        <v>12.84375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>10</v>
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12">
-        <v>689933.30661789386</v>
-      </c>
-      <c r="D12">
-        <v>730972.00272256834</v>
-      </c>
-      <c r="E12">
-        <v>53214.950129181227</v>
-      </c>
-      <c r="F12">
-        <v>56380.288206976591</v>
-      </c>
-      <c r="G12">
-        <v>12.965027777777779</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>11</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13">
-        <v>413651.5901126574</v>
-      </c>
-      <c r="D13">
-        <v>612499.03551857022</v>
-      </c>
-      <c r="E13">
-        <v>51170.403254983961</v>
-      </c>
-      <c r="F13">
-        <v>75768.650211735148</v>
-      </c>
-      <c r="G13">
-        <v>8.0838055555555552</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>12</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14">
-        <v>649285.63183478988</v>
-      </c>
-      <c r="D14">
-        <v>747801.54236852832</v>
-      </c>
-      <c r="E14">
-        <v>42695.405278231767</v>
-      </c>
-      <c r="F14">
-        <v>49173.566075823917</v>
-      </c>
-      <c r="G14">
-        <v>15.20738888888889</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>13</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15">
-        <v>600391.68688176235</v>
-      </c>
-      <c r="D15">
-        <v>530050.00639670924</v>
-      </c>
-      <c r="E15">
-        <v>55844.617423892727</v>
-      </c>
-      <c r="F15">
-        <v>49301.881537519461</v>
-      </c>
-      <c r="G15">
-        <v>10.75111111111111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>14</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16">
-        <v>479288.46818121301</v>
-      </c>
-      <c r="D16">
-        <v>398586.55678973789</v>
-      </c>
-      <c r="E16">
-        <v>39937.747330113671</v>
-      </c>
-      <c r="F16">
-        <v>33213.086170539602</v>
-      </c>
-      <c r="G16">
-        <v>12.000888888888889</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>15</v>
+        <v>72</v>
+      </c>
+      <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17">
-        <v>663654.23105805763</v>
-      </c>
-      <c r="D17">
-        <v>685281.82306254236</v>
-      </c>
-      <c r="E17">
-        <v>75326.089124584454</v>
-      </c>
-      <c r="F17">
-        <v>77780.864287070304</v>
-      </c>
-      <c r="G17">
-        <v>8.8104166666666668</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>16</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18">
-        <v>745986.55519142339</v>
-      </c>
-      <c r="D18">
-        <v>752012.10771948867</v>
-      </c>
-      <c r="E18">
-        <v>77690.297757110005</v>
-      </c>
-      <c r="F18">
-        <v>78317.825112393737</v>
-      </c>
-      <c r="G18">
-        <v>9.6020555555555553</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>17</v>
+        <v>106</v>
+      </c>
+      <c r="C18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>110</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19">
-        <v>302805.03218777431</v>
-      </c>
-      <c r="D19">
-        <v>305241.99297757412</v>
-      </c>
-      <c r="E19">
-        <v>44675.419906066592</v>
-      </c>
-      <c r="F19">
-        <v>45034.96560381251</v>
-      </c>
-      <c r="G19">
-        <v>6.7778888888888904</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20">
-        <v>421340.05261681852</v>
-      </c>
-      <c r="D20">
-        <v>391799.93556949729</v>
-      </c>
-      <c r="E20">
-        <v>59907.11501842631</v>
-      </c>
-      <c r="F20">
-        <v>55707.032024605069</v>
-      </c>
-      <c r="G20">
-        <v>7.0332222222222214</v>
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1792,724 +1785,467 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F1" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="G1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L1" t="s">
-        <v>66</v>
-      </c>
-      <c r="M1" t="s">
-        <v>67</v>
-      </c>
-      <c r="N1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>69</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>868008.31831978529</v>
       </c>
       <c r="D2">
-        <v>66661.733949396366</v>
+        <v>1000814.759840359</v>
       </c>
       <c r="E2">
-        <v>54651.677550418077</v>
+        <v>77172.872838146141</v>
       </c>
       <c r="F2">
-        <v>78671.790348374649</v>
+        <v>88980.426299607323</v>
       </c>
       <c r="G2">
-        <v>24917.92705614349</v>
-      </c>
-      <c r="H2">
+        <v>11.247583333333329</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>1111428.2606788049</v>
+      </c>
+      <c r="D3">
+        <v>1117221.440602904</v>
+      </c>
+      <c r="E3">
+        <v>87183.190178210367</v>
+      </c>
+      <c r="F3">
+        <v>87637.621584112261</v>
+      </c>
+      <c r="G3">
+        <v>12.74819444444444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>422304.31443212618</v>
+      </c>
+      <c r="D4">
+        <v>524531.94911013381</v>
+      </c>
+      <c r="E4">
+        <v>65044.389812077687</v>
+      </c>
+      <c r="F4">
+        <v>80789.751373217267</v>
+      </c>
+      <c r="G4">
+        <v>6.4925555555555556</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>444382.76247065351</v>
+      </c>
+      <c r="D5">
+        <v>344184.86684617552</v>
+      </c>
+      <c r="E5">
+        <v>54346.006029655036</v>
+      </c>
+      <c r="F5">
+        <v>42092.255660284602</v>
+      </c>
+      <c r="G5">
+        <v>8.1769166666666671</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>1520524.386244345</v>
+      </c>
+      <c r="D6">
+        <v>1568390.7439207369</v>
+      </c>
+      <c r="E6">
+        <v>108652.64760369041</v>
+      </c>
+      <c r="F6">
+        <v>112073.0508144085</v>
+      </c>
+      <c r="G6">
+        <v>13.994361111111109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>533413.82988175692</v>
+      </c>
+      <c r="D7">
+        <v>447628.65891148383</v>
+      </c>
+      <c r="E7">
+        <v>43545.763490898164</v>
+      </c>
+      <c r="F7">
+        <v>36542.6065481435</v>
+      </c>
+      <c r="G7">
+        <v>12.249499999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>582664.38348372676</v>
+      </c>
+      <c r="D8">
+        <v>933730.03242899757</v>
+      </c>
+      <c r="E8">
+        <v>48577.067545023972</v>
+      </c>
+      <c r="F8">
+        <v>77845.61428472423</v>
+      </c>
+      <c r="G8">
+        <v>11.99463888888889</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9">
+        <v>797053.15886286262</v>
+      </c>
+      <c r="D9">
+        <v>749001.71142912155</v>
+      </c>
+      <c r="E9">
         <v>56938.130086701327</v>
       </c>
-      <c r="I2">
-        <v>49873.735400003963</v>
-      </c>
-      <c r="J2">
-        <v>77431.585297628073</v>
-      </c>
-      <c r="K2">
+      <c r="F9">
+        <v>53505.536495654072</v>
+      </c>
+      <c r="G9">
+        <v>13.998583333333331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10">
+        <v>602680.2409760782</v>
+      </c>
+      <c r="D10">
+        <v>566191.97830694204</v>
+      </c>
+      <c r="E10">
+        <v>135224.42582730119</v>
+      </c>
+      <c r="F10">
+        <v>127037.4901466513</v>
+      </c>
+      <c r="G10">
+        <v>4.4568888888888889</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11">
+        <v>1148570.4072544051</v>
+      </c>
+      <c r="D11">
+        <v>1111210.7757937161</v>
+      </c>
+      <c r="E11">
+        <v>89426.406404235895</v>
+      </c>
+      <c r="F11">
+        <v>86517.627312406097</v>
+      </c>
+      <c r="G11">
+        <v>12.84375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12">
+        <v>689933.30661789386</v>
+      </c>
+      <c r="D12">
+        <v>730972.00272256834</v>
+      </c>
+      <c r="E12">
+        <v>53214.950129181227</v>
+      </c>
+      <c r="F12">
+        <v>56380.288206976591</v>
+      </c>
+      <c r="G12">
+        <v>12.965027777777779</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13">
+        <v>413651.5901126574</v>
+      </c>
+      <c r="D13">
+        <v>612499.03551857022</v>
+      </c>
+      <c r="E13">
+        <v>51170.403254983961</v>
+      </c>
+      <c r="F13">
+        <v>75768.650211735148</v>
+      </c>
+      <c r="G13">
+        <v>8.0838055555555552</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14">
+        <v>649285.63183478988</v>
+      </c>
+      <c r="D14">
+        <v>747801.54236852832</v>
+      </c>
+      <c r="E14">
+        <v>42695.405278231767</v>
+      </c>
+      <c r="F14">
+        <v>49173.566075823917</v>
+      </c>
+      <c r="G14">
+        <v>15.20738888888889</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15">
+        <v>600391.68688176235</v>
+      </c>
+      <c r="D15">
+        <v>530050.00639670924</v>
+      </c>
+      <c r="E15">
+        <v>55844.617423892727</v>
+      </c>
+      <c r="F15">
+        <v>49301.881537519461</v>
+      </c>
+      <c r="G15">
+        <v>10.75111111111111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16">
+        <v>479288.46818121301</v>
+      </c>
+      <c r="D16">
+        <v>398586.55678973789</v>
+      </c>
+      <c r="E16">
         <v>39937.747330113671</v>
       </c>
-      <c r="L2">
-        <v>135224.42582730119</v>
-      </c>
-      <c r="M2">
-        <v>1.2826405065577851</v>
-      </c>
-      <c r="N2">
-        <v>1.393792601950105E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3">
-        <v>19</v>
-      </c>
-      <c r="D3">
-        <v>69142.112618404513</v>
-      </c>
-      <c r="E3">
-        <v>56857.356285190159</v>
-      </c>
-      <c r="F3">
-        <v>81426.868951618875</v>
-      </c>
-      <c r="G3">
-        <v>25487.86217519956</v>
-      </c>
-      <c r="H3">
-        <v>75768.650211735148</v>
-      </c>
-      <c r="I3">
-        <v>49237.723806671696</v>
-      </c>
-      <c r="J3">
-        <v>83653.689342811675</v>
-      </c>
-      <c r="K3">
+      <c r="F16">
         <v>33213.086170539602</v>
       </c>
-      <c r="L3">
-        <v>127037.4901466513</v>
-      </c>
-      <c r="M3">
-        <v>0.54322748333829018</v>
-      </c>
-      <c r="N3">
-        <v>0.2480084803447237</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>-2480.3786690081361</v>
-      </c>
-      <c r="E4">
-        <v>-7802.54594682279</v>
-      </c>
-      <c r="F4">
-        <v>2841.7886088065179</v>
-      </c>
-      <c r="G4">
-        <v>11042.194274829661</v>
-      </c>
-      <c r="H4">
-        <v>-454.43140590189432</v>
-      </c>
-      <c r="I4">
-        <v>-4949.2820041550949</v>
-      </c>
-      <c r="J4">
-        <v>5371.4094400972572</v>
-      </c>
-      <c r="K4">
-        <v>-29268.546739700261</v>
-      </c>
-      <c r="L4">
-        <v>12253.750369370429</v>
-      </c>
-      <c r="M4">
-        <v>-1.093263132431763</v>
-      </c>
-      <c r="N4">
-        <v>3.5634645491596111E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>65151.56025544431</v>
-      </c>
-      <c r="E5">
-        <v>51405.899193418401</v>
-      </c>
-      <c r="F5">
-        <v>78897.221317470219</v>
-      </c>
-      <c r="G5">
-        <v>20460.663929223971</v>
-      </c>
-      <c r="H5">
+      <c r="G16">
+        <v>12.000888888888889</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17">
+        <v>663654.23105805763</v>
+      </c>
+      <c r="D17">
+        <v>685281.82306254236</v>
+      </c>
+      <c r="E17">
+        <v>75326.089124584454</v>
+      </c>
+      <c r="F17">
+        <v>77780.864287070304</v>
+      </c>
+      <c r="G17">
+        <v>8.8104166666666668</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18">
+        <v>745986.55519142339</v>
+      </c>
+      <c r="D18">
+        <v>752012.10771948867</v>
+      </c>
+      <c r="E18">
+        <v>77690.297757110005</v>
+      </c>
+      <c r="F18">
+        <v>78317.825112393737</v>
+      </c>
+      <c r="G18">
+        <v>9.6020555555555553</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19">
+        <v>302805.03218777431</v>
+      </c>
+      <c r="D19">
+        <v>305241.99297757412</v>
+      </c>
+      <c r="E19">
+        <v>44675.419906066592</v>
+      </c>
+      <c r="F19">
+        <v>45034.96560381251</v>
+      </c>
+      <c r="G19">
+        <v>6.7778888888888904</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20">
+        <v>421340.05261681852</v>
+      </c>
+      <c r="D20">
+        <v>391799.93556949729</v>
+      </c>
+      <c r="E20">
         <v>59907.11501842631</v>
       </c>
-      <c r="I5">
-        <v>51461.536787339501</v>
-      </c>
-      <c r="J5">
-        <v>76249.480981365297</v>
-      </c>
-      <c r="K5">
-        <v>39937.747330113671</v>
-      </c>
-      <c r="L5">
-        <v>108652.64760369041</v>
-      </c>
-      <c r="M5">
-        <v>0.78883043176696921</v>
-      </c>
-      <c r="N5">
-        <v>0.50415102695834058</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>68223.322694536459</v>
-      </c>
-      <c r="E6">
-        <v>51721.75784805174</v>
-      </c>
-      <c r="F6">
-        <v>84724.887541021177</v>
-      </c>
-      <c r="G6">
-        <v>24562.876321967</v>
-      </c>
-      <c r="H6">
-        <v>77780.864287070304</v>
-      </c>
-      <c r="I6">
-        <v>47168.423570665982</v>
-      </c>
-      <c r="J6">
-        <v>84213.686478664764</v>
-      </c>
-      <c r="K6">
-        <v>33213.086170539602</v>
-      </c>
-      <c r="L6">
-        <v>112073.0508144085</v>
-      </c>
-      <c r="M6">
-        <v>0.15827549427390561</v>
-      </c>
-      <c r="N6">
-        <v>0.54536645924349281</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7">
-        <v>11</v>
-      </c>
-      <c r="D7">
-        <v>-3071.7624390921542</v>
-      </c>
-      <c r="E7">
-        <v>-11060.570338827671</v>
-      </c>
-      <c r="F7">
-        <v>4917.0454606433559</v>
-      </c>
-      <c r="G7">
-        <v>11891.48436688768</v>
-      </c>
-      <c r="H7">
-        <v>-454.43140590189432</v>
-      </c>
-      <c r="I7">
-        <v>-7613.9783360896108</v>
-      </c>
-      <c r="J7">
-        <v>5371.4094400972572</v>
-      </c>
-      <c r="K7">
-        <v>-29268.546739700261</v>
-      </c>
-      <c r="L7">
-        <v>12253.750369370429</v>
-      </c>
-      <c r="M7">
-        <v>-0.92493369088769495</v>
-      </c>
-      <c r="N7">
-        <v>0.32686346556939488</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8">
-        <v>8</v>
-      </c>
-      <c r="D8">
-        <v>68738.222778580443</v>
-      </c>
-      <c r="E8">
-        <v>42432.894659345082</v>
-      </c>
-      <c r="F8">
-        <v>95043.550897815803</v>
-      </c>
-      <c r="G8">
-        <v>31464.91605491958</v>
-      </c>
-      <c r="H8">
-        <v>55076.540107941277</v>
-      </c>
-      <c r="I8">
-        <v>49264.243313962506</v>
-      </c>
-      <c r="J8">
-        <v>80624.324918891478</v>
-      </c>
-      <c r="K8">
-        <v>42695.405278231767</v>
-      </c>
-      <c r="L8">
-        <v>135224.42582730119</v>
-      </c>
-      <c r="M8">
-        <v>1.2698046810593959</v>
-      </c>
-      <c r="N8">
-        <v>4.5871257764425501E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="D9">
-        <v>70405.448763723049</v>
-      </c>
-      <c r="E9">
-        <v>46679.203778484611</v>
-      </c>
-      <c r="F9">
-        <v>94131.693748961494</v>
-      </c>
-      <c r="G9">
-        <v>28379.965586252671</v>
-      </c>
-      <c r="H9">
-        <v>66074.46920935587</v>
-      </c>
-      <c r="I9">
-        <v>52422.543890696543</v>
-      </c>
-      <c r="J9">
-        <v>80367.775662396831</v>
-      </c>
-      <c r="K9">
-        <v>36542.6065481435</v>
-      </c>
-      <c r="L9">
-        <v>127037.4901466513</v>
-      </c>
-      <c r="M9">
-        <v>0.87174540457038263</v>
-      </c>
-      <c r="N9">
-        <v>0.42710811618418781</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10">
-        <v>8</v>
-      </c>
-      <c r="D10">
-        <v>-1667.2259851426111</v>
-      </c>
-      <c r="E10">
-        <v>-10444.195261706771</v>
-      </c>
-      <c r="F10">
-        <v>7109.7432914215506</v>
-      </c>
-      <c r="G10">
-        <v>10498.504342994949</v>
-      </c>
-      <c r="H10">
-        <v>1140.6258682730329</v>
-      </c>
-      <c r="I10">
-        <v>-3993.543757744555</v>
-      </c>
-      <c r="J10">
-        <v>4325.2344289741104</v>
-      </c>
-      <c r="K10">
-        <v>-24598.246956751191</v>
-      </c>
-      <c r="L10">
-        <v>8186.9356806498254</v>
-      </c>
-      <c r="M10">
-        <v>-1.3639450823200769</v>
-      </c>
-      <c r="N10">
-        <v>7.5180915138518503E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11">
-        <v>15</v>
-      </c>
-      <c r="D11">
-        <v>69904.408953150923</v>
-      </c>
-      <c r="E11">
-        <v>54906.913996463467</v>
-      </c>
-      <c r="F11">
-        <v>84901.90390983838</v>
-      </c>
-      <c r="G11">
-        <v>27081.96974985435</v>
-      </c>
-      <c r="H11">
-        <v>59907.11501842631</v>
-      </c>
-      <c r="I11">
-        <v>49510.712967860818</v>
-      </c>
-      <c r="J11">
-        <v>82436.743967660179</v>
-      </c>
-      <c r="K11">
-        <v>39937.747330113671</v>
-      </c>
-      <c r="L11">
-        <v>135224.42582730119</v>
-      </c>
-      <c r="M11">
-        <v>0.965355145714486</v>
-      </c>
-      <c r="N11">
-        <v>9.6162526248829427E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12">
-        <v>15</v>
-      </c>
-      <c r="D12">
-        <v>68194.389044868818</v>
-      </c>
-      <c r="E12">
-        <v>52488.001244999323</v>
-      </c>
-      <c r="F12">
-        <v>83900.776844738313</v>
-      </c>
-      <c r="G12">
-        <v>28362.064498369899</v>
-      </c>
-      <c r="H12">
+      <c r="F20">
         <v>55707.032024605069</v>
       </c>
-      <c r="I12">
-        <v>47104.265839818218</v>
-      </c>
-      <c r="J12">
-        <v>87077.624448259186</v>
-      </c>
-      <c r="K12">
-        <v>33213.086170539602</v>
-      </c>
-      <c r="L12">
-        <v>127037.4901466513</v>
-      </c>
-      <c r="M12">
-        <v>0.61302648302567386</v>
-      </c>
-      <c r="N12">
-        <v>0.17784443924573851</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13">
-        <v>15</v>
-      </c>
-      <c r="D13">
-        <v>1710.01990828212</v>
-      </c>
-      <c r="E13">
-        <v>-1755.034511212973</v>
-      </c>
-      <c r="F13">
-        <v>5175.0743277772117</v>
-      </c>
-      <c r="G13">
-        <v>6257.078214820217</v>
-      </c>
-      <c r="H13">
-        <v>2908.7790918297978</v>
-      </c>
-      <c r="I13">
-        <v>-1541.1512588847911</v>
-      </c>
-      <c r="J13">
-        <v>6633.6985229736711</v>
-      </c>
-      <c r="K13">
-        <v>-11807.553461461181</v>
-      </c>
-      <c r="L13">
-        <v>12253.750369370429</v>
-      </c>
-      <c r="M13">
-        <v>-0.42393888947224301</v>
-      </c>
-      <c r="N13">
-        <v>0.91698671245046559</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>54501.702685316719</v>
-      </c>
-      <c r="E14">
-        <v>42917.319766867833</v>
-      </c>
-      <c r="F14">
-        <v>66086.085603765605</v>
-      </c>
-      <c r="G14">
-        <v>7280.1749391439716</v>
-      </c>
-      <c r="H14">
-        <v>52192.676692082598</v>
-      </c>
-      <c r="I14">
-        <v>50522.069327493962</v>
-      </c>
-      <c r="J14">
-        <v>56172.310049905347</v>
-      </c>
-      <c r="K14">
-        <v>48577.067545023972</v>
-      </c>
-      <c r="L14">
-        <v>65044.389812077687</v>
-      </c>
-      <c r="M14">
-        <v>0.92244792960339217</v>
-      </c>
-      <c r="N14">
-        <v>0.24168878217532749</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15">
-        <v>72696.076019163316</v>
-      </c>
-      <c r="E15">
-        <v>55080.366840377414</v>
-      </c>
-      <c r="F15">
-        <v>90311.785197949226</v>
-      </c>
-      <c r="G15">
-        <v>11070.54604474498</v>
-      </c>
-      <c r="H15">
-        <v>76807.132248229696</v>
-      </c>
-      <c r="I15">
-        <v>70921.559710545509</v>
-      </c>
-      <c r="J15">
-        <v>78581.648556847489</v>
-      </c>
-      <c r="K15">
-        <v>56380.288206976591</v>
-      </c>
-      <c r="L15">
-        <v>80789.751373217267</v>
-      </c>
-      <c r="M15">
-        <v>-1.0347760465965641</v>
-      </c>
-      <c r="N15">
-        <v>9.7429203444657109E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16">
-        <v>4</v>
-      </c>
-      <c r="D16">
-        <v>-18194.37333384659</v>
-      </c>
-      <c r="E16">
-        <v>-36464.970833980908</v>
-      </c>
-      <c r="F16">
-        <v>76.224166287720436</v>
-      </c>
-      <c r="G16">
-        <v>11482.10888573376</v>
-      </c>
-      <c r="H16">
-        <v>-20171.80425894538</v>
-      </c>
-      <c r="I16">
-        <v>-25765.821902488449</v>
-      </c>
-      <c r="J16">
-        <v>-12600.355690303521</v>
-      </c>
-      <c r="K16">
-        <v>-29268.546739700261</v>
-      </c>
-      <c r="L16">
-        <v>-3165.3380777953571</v>
-      </c>
-      <c r="M16">
-        <v>0.45477423161515118</v>
-      </c>
-      <c r="N16">
-        <v>0.73350902826616171</v>
+      <c r="G20">
+        <v>7.0332222222222214</v>
       </c>
     </row>
   </sheetData>
@@ -2519,166 +2255,711 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="B1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
-        <v>58</v>
-      </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="E1" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="F1" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="G1" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="H1" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="I1" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="J1" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="K1" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="L1" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="M1" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="N1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P1" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2">
+        <v>130</v>
+      </c>
+      <c r="B2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2">
         <v>19</v>
       </c>
-      <c r="C2">
-        <v>684071.92722562805</v>
-      </c>
       <c r="D2">
-        <v>302964.47512733599</v>
+        <v>66661.733949396366</v>
       </c>
       <c r="E2">
-        <v>0.44288394694993682</v>
+        <v>54651.677550418077</v>
       </c>
       <c r="F2">
-        <v>-1.0650442012426431</v>
+        <v>78671.790348374649</v>
       </c>
       <c r="G2">
-        <v>0.30093478417096808</v>
+        <v>24917.92705614349</v>
       </c>
       <c r="H2">
-        <v>18</v>
+        <v>56938.130086701327</v>
       </c>
       <c r="I2">
-        <v>-27357.121212044862</v>
-      </c>
-      <c r="J2" t="s">
-        <v>92</v>
+        <v>49873.735400003963</v>
+      </c>
+      <c r="J2">
+        <v>77431.585297628073</v>
       </c>
       <c r="K2">
-        <v>-81322.185614884977</v>
+        <v>39937.747330113671</v>
       </c>
       <c r="L2">
-        <v>26607.94319079526</v>
-      </c>
-      <c r="M2" t="s">
-        <v>93</v>
+        <v>135224.42582730119</v>
+      </c>
+      <c r="M2">
+        <v>1.2826405065577851</v>
       </c>
       <c r="N2">
-        <v>1.8036640996328641E-2</v>
-      </c>
-      <c r="O2">
-        <v>-1.3838525082056661</v>
-      </c>
-      <c r="P2">
-        <v>0.54121780395507813</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.393792601950105E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3">
+        <v>130</v>
+      </c>
+      <c r="B3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3">
         <v>19</v>
       </c>
-      <c r="C3">
-        <v>711429.04843767302</v>
-      </c>
       <c r="D3">
-        <v>321945.06104520359</v>
+        <v>69142.112618404513</v>
       </c>
       <c r="E3">
-        <v>0.45253291491570102</v>
+        <v>56857.356285190159</v>
       </c>
       <c r="F3">
-        <v>-1.0650442012426431</v>
+        <v>81426.868951618875</v>
       </c>
       <c r="G3">
-        <v>0.30093478417096808</v>
+        <v>25487.86217519956</v>
       </c>
       <c r="H3">
-        <v>18</v>
+        <v>75768.650211735148</v>
       </c>
       <c r="I3">
-        <v>-27357.121212044862</v>
-      </c>
-      <c r="J3" t="s">
-        <v>92</v>
+        <v>49237.723806671696</v>
+      </c>
+      <c r="J3">
+        <v>83653.689342811675</v>
       </c>
       <c r="K3">
-        <v>-81322.185614884977</v>
+        <v>33213.086170539602</v>
       </c>
       <c r="L3">
-        <v>26607.94319079526</v>
-      </c>
-      <c r="M3" t="s">
-        <v>93</v>
+        <v>127037.4901466513</v>
+      </c>
+      <c r="M3">
+        <v>0.54322748333829018</v>
       </c>
       <c r="N3">
-        <v>1.8036640996328641E-2</v>
-      </c>
-      <c r="O3">
-        <v>-1.3838525082056661</v>
-      </c>
-      <c r="P3">
-        <v>0.54121780395507813</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>94</v>
+        <v>0.2480084803447237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>-2480.3786690081361</v>
+      </c>
+      <c r="E4">
+        <v>-7802.54594682279</v>
+      </c>
+      <c r="F4">
+        <v>2841.7886088065179</v>
+      </c>
+      <c r="G4">
+        <v>11042.194274829661</v>
+      </c>
+      <c r="H4">
+        <v>-454.43140590189432</v>
+      </c>
+      <c r="I4">
+        <v>-4949.2820041550949</v>
+      </c>
+      <c r="J4">
+        <v>5371.4094400972572</v>
+      </c>
+      <c r="K4">
+        <v>-29268.546739700261</v>
+      </c>
+      <c r="L4">
+        <v>12253.750369370429</v>
+      </c>
+      <c r="M4">
+        <v>-1.093263132431763</v>
+      </c>
+      <c r="N4">
+        <v>3.5634645491596111E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>65151.56025544431</v>
+      </c>
+      <c r="E5">
+        <v>51405.899193418401</v>
+      </c>
+      <c r="F5">
+        <v>78897.221317470219</v>
+      </c>
+      <c r="G5">
+        <v>20460.663929223971</v>
+      </c>
+      <c r="H5">
+        <v>59907.11501842631</v>
+      </c>
+      <c r="I5">
+        <v>51461.536787339501</v>
+      </c>
+      <c r="J5">
+        <v>76249.480981365297</v>
+      </c>
+      <c r="K5">
+        <v>39937.747330113671</v>
+      </c>
+      <c r="L5">
+        <v>108652.64760369041</v>
+      </c>
+      <c r="M5">
+        <v>0.78883043176696921</v>
+      </c>
+      <c r="N5">
+        <v>0.50415102695834058</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>68223.322694536459</v>
+      </c>
+      <c r="E6">
+        <v>51721.75784805174</v>
+      </c>
+      <c r="F6">
+        <v>84724.887541021177</v>
+      </c>
+      <c r="G6">
+        <v>24562.876321967</v>
+      </c>
+      <c r="H6">
+        <v>77780.864287070304</v>
+      </c>
+      <c r="I6">
+        <v>47168.423570665982</v>
+      </c>
+      <c r="J6">
+        <v>84213.686478664764</v>
+      </c>
+      <c r="K6">
+        <v>33213.086170539602</v>
+      </c>
+      <c r="L6">
+        <v>112073.0508144085</v>
+      </c>
+      <c r="M6">
+        <v>0.15827549427390561</v>
+      </c>
+      <c r="N6">
+        <v>0.54536645924349281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>-3071.7624390921542</v>
+      </c>
+      <c r="E7">
+        <v>-11060.570338827671</v>
+      </c>
+      <c r="F7">
+        <v>4917.0454606433559</v>
+      </c>
+      <c r="G7">
+        <v>11891.48436688768</v>
+      </c>
+      <c r="H7">
+        <v>-454.43140590189432</v>
+      </c>
+      <c r="I7">
+        <v>-7613.9783360896108</v>
+      </c>
+      <c r="J7">
+        <v>5371.4094400972572</v>
+      </c>
+      <c r="K7">
+        <v>-29268.546739700261</v>
+      </c>
+      <c r="L7">
+        <v>12253.750369370429</v>
+      </c>
+      <c r="M7">
+        <v>-0.92493369088769495</v>
+      </c>
+      <c r="N7">
+        <v>0.32686346556939488</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>68738.222778580443</v>
+      </c>
+      <c r="E8">
+        <v>42432.894659345082</v>
+      </c>
+      <c r="F8">
+        <v>95043.550897815803</v>
+      </c>
+      <c r="G8">
+        <v>31464.91605491958</v>
+      </c>
+      <c r="H8">
+        <v>55076.540107941277</v>
+      </c>
+      <c r="I8">
+        <v>49264.243313962506</v>
+      </c>
+      <c r="J8">
+        <v>80624.324918891478</v>
+      </c>
+      <c r="K8">
+        <v>42695.405278231767</v>
+      </c>
+      <c r="L8">
+        <v>135224.42582730119</v>
+      </c>
+      <c r="M8">
+        <v>1.2698046810593959</v>
+      </c>
+      <c r="N8">
+        <v>4.5871257764425501E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>70405.448763723049</v>
+      </c>
+      <c r="E9">
+        <v>46679.203778484611</v>
+      </c>
+      <c r="F9">
+        <v>94131.693748961494</v>
+      </c>
+      <c r="G9">
+        <v>28379.965586252671</v>
+      </c>
+      <c r="H9">
+        <v>66074.46920935587</v>
+      </c>
+      <c r="I9">
+        <v>52422.543890696543</v>
+      </c>
+      <c r="J9">
+        <v>80367.775662396831</v>
+      </c>
+      <c r="K9">
+        <v>36542.6065481435</v>
+      </c>
+      <c r="L9">
+        <v>127037.4901466513</v>
+      </c>
+      <c r="M9">
+        <v>0.87174540457038263</v>
+      </c>
+      <c r="N9">
+        <v>0.42710811618418781</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>-1667.2259851426111</v>
+      </c>
+      <c r="E10">
+        <v>-10444.195261706771</v>
+      </c>
+      <c r="F10">
+        <v>7109.7432914215506</v>
+      </c>
+      <c r="G10">
+        <v>10498.504342994949</v>
+      </c>
+      <c r="H10">
+        <v>1140.6258682730329</v>
+      </c>
+      <c r="I10">
+        <v>-3993.543757744555</v>
+      </c>
+      <c r="J10">
+        <v>4325.2344289741104</v>
+      </c>
+      <c r="K10">
+        <v>-24598.246956751191</v>
+      </c>
+      <c r="L10">
+        <v>8186.9356806498254</v>
+      </c>
+      <c r="M10">
+        <v>-1.3639450823200769</v>
+      </c>
+      <c r="N10">
+        <v>7.5180915138518503E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>69904.408953150923</v>
+      </c>
+      <c r="E11">
+        <v>54906.913996463467</v>
+      </c>
+      <c r="F11">
+        <v>84901.90390983838</v>
+      </c>
+      <c r="G11">
+        <v>27081.96974985435</v>
+      </c>
+      <c r="H11">
+        <v>59907.11501842631</v>
+      </c>
+      <c r="I11">
+        <v>49510.712967860818</v>
+      </c>
+      <c r="J11">
+        <v>82436.743967660179</v>
+      </c>
+      <c r="K11">
+        <v>39937.747330113671</v>
+      </c>
+      <c r="L11">
+        <v>135224.42582730119</v>
+      </c>
+      <c r="M11">
+        <v>0.965355145714486</v>
+      </c>
+      <c r="N11">
+        <v>9.6162526248829427E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>68194.389044868818</v>
+      </c>
+      <c r="E12">
+        <v>52488.001244999323</v>
+      </c>
+      <c r="F12">
+        <v>83900.776844738313</v>
+      </c>
+      <c r="G12">
+        <v>28362.064498369899</v>
+      </c>
+      <c r="H12">
+        <v>55707.032024605069</v>
+      </c>
+      <c r="I12">
+        <v>47104.265839818218</v>
+      </c>
+      <c r="J12">
+        <v>87077.624448259186</v>
+      </c>
+      <c r="K12">
+        <v>33213.086170539602</v>
+      </c>
+      <c r="L12">
+        <v>127037.4901466513</v>
+      </c>
+      <c r="M12">
+        <v>0.61302648302567386</v>
+      </c>
+      <c r="N12">
+        <v>0.17784443924573851</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>1710.01990828212</v>
+      </c>
+      <c r="E13">
+        <v>-1755.034511212973</v>
+      </c>
+      <c r="F13">
+        <v>5175.0743277772117</v>
+      </c>
+      <c r="G13">
+        <v>6257.078214820217</v>
+      </c>
+      <c r="H13">
+        <v>2908.7790918297978</v>
+      </c>
+      <c r="I13">
+        <v>-1541.1512588847911</v>
+      </c>
+      <c r="J13">
+        <v>6633.6985229736711</v>
+      </c>
+      <c r="K13">
+        <v>-11807.553461461181</v>
+      </c>
+      <c r="L13">
+        <v>12253.750369370429</v>
+      </c>
+      <c r="M13">
+        <v>-0.42393888947224301</v>
+      </c>
+      <c r="N13">
+        <v>0.91698671245046559</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>54501.702685316719</v>
+      </c>
+      <c r="E14">
+        <v>42917.319766867833</v>
+      </c>
+      <c r="F14">
+        <v>66086.085603765605</v>
+      </c>
+      <c r="G14">
+        <v>7280.1749391439716</v>
+      </c>
+      <c r="H14">
+        <v>52192.676692082598</v>
+      </c>
+      <c r="I14">
+        <v>50522.069327493962</v>
+      </c>
+      <c r="J14">
+        <v>56172.310049905347</v>
+      </c>
+      <c r="K14">
+        <v>48577.067545023972</v>
+      </c>
+      <c r="L14">
+        <v>65044.389812077687</v>
+      </c>
+      <c r="M14">
+        <v>0.92244792960339217</v>
+      </c>
+      <c r="N14">
+        <v>0.24168878217532749</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <v>72696.076019163316</v>
+      </c>
+      <c r="E15">
+        <v>55080.366840377414</v>
+      </c>
+      <c r="F15">
+        <v>90311.785197949226</v>
+      </c>
+      <c r="G15">
+        <v>11070.54604474498</v>
+      </c>
+      <c r="H15">
+        <v>76807.132248229696</v>
+      </c>
+      <c r="I15">
+        <v>70921.559710545509</v>
+      </c>
+      <c r="J15">
+        <v>78581.648556847489</v>
+      </c>
+      <c r="K15">
+        <v>56380.288206976591</v>
+      </c>
+      <c r="L15">
+        <v>80789.751373217267</v>
+      </c>
+      <c r="M15">
+        <v>-1.0347760465965641</v>
+      </c>
+      <c r="N15">
+        <v>9.7429203444657109E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16">
+        <v>-18194.37333384659</v>
+      </c>
+      <c r="E16">
+        <v>-36464.970833980908</v>
+      </c>
+      <c r="F16">
+        <v>76.224166287720436</v>
+      </c>
+      <c r="G16">
+        <v>11482.10888573376</v>
+      </c>
+      <c r="H16">
+        <v>-20171.80425894538</v>
+      </c>
+      <c r="I16">
+        <v>-25765.821902488449</v>
+      </c>
+      <c r="J16">
+        <v>-12600.355690303521</v>
+      </c>
+      <c r="K16">
+        <v>-29268.546739700261</v>
+      </c>
+      <c r="L16">
+        <v>-3165.3380777953571</v>
+      </c>
+      <c r="M16">
+        <v>0.45477423161515118</v>
+      </c>
+      <c r="N16">
+        <v>0.73350902826616171</v>
       </c>
     </row>
   </sheetData>
@@ -2690,181 +2971,164 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="40.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="B1" t="s">
         <v>57</v>
       </c>
       <c r="C1" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="E1" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="F1" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="G1" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="H1" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="I1" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="J1" t="s">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="K1" t="s">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="L1" t="s">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="M1" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="N1" t="s">
-        <v>87</v>
+        <v>148</v>
       </c>
       <c r="O1" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="P1" t="s">
-        <v>89</v>
+        <v>150</v>
       </c>
       <c r="Q1" t="s">
-        <v>90</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="B2">
         <v>19</v>
       </c>
       <c r="C2">
-        <v>66661.733949396366</v>
+        <v>684071.92722562805</v>
       </c>
       <c r="D2">
-        <v>24917.92705614349</v>
+        <v>302964.47512733599</v>
       </c>
       <c r="E2">
-        <v>0.37379656333360539</v>
+        <v>0.44288394694993682</v>
       </c>
       <c r="F2">
-        <v>-0.97912785184058648</v>
+        <v>-1.0650442012426431</v>
       </c>
       <c r="G2">
-        <v>0.34049425859165489</v>
+        <v>0.30093478417096808</v>
       </c>
       <c r="H2">
         <v>18</v>
       </c>
       <c r="I2">
-        <v>-2480.3786690081361</v>
+        <v>-27357.121212044862</v>
       </c>
       <c r="J2" t="s">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="K2">
-        <v>-7802.54594682279</v>
+        <v>-81322.185614884977</v>
       </c>
       <c r="L2">
-        <v>2841.7886088065179</v>
+        <v>26607.94319079526</v>
       </c>
       <c r="M2" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="N2">
-        <v>3.5634645491596111E-2</v>
+        <v>1.8036640996328641E-2</v>
       </c>
       <c r="O2">
-        <v>-1.093263132431763</v>
+        <v>-1.3838525082056661</v>
       </c>
       <c r="P2">
-        <v>0.79825210571289063</v>
+        <v>0.54121780395507813</v>
       </c>
       <c r="Q2" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="B3">
         <v>19</v>
       </c>
       <c r="C3">
-        <v>69142.112618404513</v>
+        <v>711429.04843767302</v>
       </c>
       <c r="D3">
-        <v>25487.86217519956</v>
+        <v>321945.06104520359</v>
       </c>
       <c r="E3">
-        <v>0.3686300752172143</v>
+        <v>0.45253291491570102</v>
       </c>
       <c r="F3">
-        <v>-0.97912785184058648</v>
+        <v>-1.0650442012426431</v>
       </c>
       <c r="G3">
-        <v>0.34049425859165489</v>
+        <v>0.30093478417096808</v>
       </c>
       <c r="H3">
         <v>18</v>
       </c>
       <c r="I3">
-        <v>-2480.3786690081361</v>
+        <v>-27357.121212044862</v>
       </c>
       <c r="J3" t="s">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="K3">
-        <v>-7802.54594682279</v>
+        <v>-81322.185614884977</v>
       </c>
       <c r="L3">
-        <v>2841.7886088065179</v>
+        <v>26607.94319079526</v>
       </c>
       <c r="M3" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="N3">
-        <v>3.5634645491596111E-2</v>
+        <v>1.8036640996328641E-2</v>
       </c>
       <c r="O3">
-        <v>-1.093263132431763</v>
+        <v>-1.3838525082056661</v>
       </c>
       <c r="P3">
-        <v>0.79825210571289063</v>
+        <v>0.54121780395507813</v>
       </c>
       <c r="Q3" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2874,79 +3138,234 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M1" t="s">
+        <v>147</v>
+      </c>
+      <c r="N1" t="s">
+        <v>148</v>
+      </c>
+      <c r="O1" t="s">
+        <v>149</v>
+      </c>
+      <c r="P1" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2">
+        <v>19</v>
+      </c>
+      <c r="C2">
+        <v>66661.733949396366</v>
+      </c>
+      <c r="D2">
+        <v>24917.92705614349</v>
+      </c>
+      <c r="E2">
+        <v>0.37379656333360539</v>
+      </c>
+      <c r="F2">
+        <v>-0.97912785184058648</v>
+      </c>
+      <c r="G2">
+        <v>0.34049425859165489</v>
+      </c>
+      <c r="H2">
+        <v>18</v>
+      </c>
+      <c r="I2">
+        <v>-2480.3786690081361</v>
+      </c>
+      <c r="J2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K2">
+        <v>-7802.54594682279</v>
+      </c>
+      <c r="L2">
+        <v>2841.7886088065179</v>
+      </c>
+      <c r="M2" t="s">
+        <v>154</v>
+      </c>
+      <c r="N2">
+        <v>3.5634645491596111E-2</v>
+      </c>
+      <c r="O2">
+        <v>-1.093263132431763</v>
+      </c>
+      <c r="P2">
+        <v>0.79825210571289063</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3">
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <v>69142.112618404513</v>
+      </c>
+      <c r="D3">
+        <v>25487.86217519956</v>
+      </c>
+      <c r="E3">
+        <v>0.3686300752172143</v>
+      </c>
+      <c r="F3">
+        <v>-0.97912785184058648</v>
+      </c>
+      <c r="G3">
+        <v>0.34049425859165489</v>
+      </c>
+      <c r="H3">
+        <v>18</v>
+      </c>
+      <c r="I3">
+        <v>-2480.3786690081361</v>
+      </c>
+      <c r="J3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K3">
+        <v>-7802.54594682279</v>
+      </c>
+      <c r="L3">
+        <v>2841.7886088065179</v>
+      </c>
+      <c r="M3" t="s">
+        <v>154</v>
+      </c>
+      <c r="N3">
+        <v>3.5634645491596111E-2</v>
+      </c>
+      <c r="O3">
+        <v>-1.093263132431763</v>
+      </c>
+      <c r="P3">
+        <v>0.79825210571289063</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="102.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="B1" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="C1" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="D1" t="s">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="E1" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="F1" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="G1" t="s">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="H1" t="s">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="I1" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="J1" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="K1" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="L1" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="M1" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="N1" t="s">
-        <v>90</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="C2">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="E2">
         <v>-2480.378669008137</v>
@@ -2976,21 +3395,21 @@
         <v>3.5634645491596111E-2</v>
       </c>
       <c r="N2" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="C3">
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="E3">
         <v>-2369.4942121173831</v>
@@ -3020,21 +3439,21 @@
         <v>3.9045432939055803E-2</v>
       </c>
       <c r="N3" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="C4">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="E4">
         <v>1404.5364539495449</v>
@@ -3064,21 +3483,21 @@
         <v>3.9045432939055803E-2</v>
       </c>
       <c r="N4" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="C5">
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="E5">
         <v>-8242.1767127822404</v>
@@ -3108,21 +3527,21 @@
         <v>0.99526094138010168</v>
       </c>
       <c r="N5" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="C6">
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>174</v>
       </c>
       <c r="E6">
         <v>19904.393242128721</v>
@@ -3152,21 +3571,21 @@
         <v>0.99526094138010168</v>
       </c>
       <c r="N6" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="C7">
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="E7">
         <v>-8103.1460678163703</v>
@@ -3196,21 +3615,21 @@
         <v>0.84830261441856725</v>
       </c>
       <c r="N7" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="C8">
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="E8">
         <v>2780.6128993173088</v>
@@ -3240,21 +3659,21 @@
         <v>0.84830261441856725</v>
       </c>
       <c r="N8" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="C9">
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>174</v>
       </c>
       <c r="E9">
         <v>20182.45453206043</v>
@@ -3284,7 +3703,7 @@
         <v>0.84830261441856725</v>
       </c>
       <c r="N9" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/statistics_output.xlsx
+++ b/outputs/statistics_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Documents\School\THESIS\Publications\Third Submission\New Analysis\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD680356-8208-4F73-A5FE-EAA2CE478CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C2C55C-C4D9-4CB7-B6C0-391A10D2DD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="raw_demographics" sheetId="1" r:id="rId1"/>
@@ -898,6 +898,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2257,6 +2268,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2971,6 +2995,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -3140,6 +3181,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -3309,6 +3367,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="102.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/outputs/statistics_output.xlsx
+++ b/outputs/statistics_output.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C2C55C-C4D9-4CB7-B6C0-391A10D2DD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="raw_demographics" sheetId="1" r:id="rId1"/>

--- a/outputs/statistics_output.xlsx
+++ b/outputs/statistics_output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Documents\School\THESIS\Publications\Third Submission\New Analysis\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C2C55C-C4D9-4CB7-B6C0-391A10D2DD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB4553F-D6AE-4F28-BD12-1722D46AE930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="raw_demographics" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,25 @@
     <sheet name="rotation_rate_stats" sheetId="6" r:id="rId6"/>
     <sheet name="difference_model_stats" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="178">
   <si>
     <t>participant</t>
   </si>
@@ -557,12 +570,19 @@
   </si>
   <si>
     <t>difference ~ sex_m_vs_f + dominant_vs_nondominant_surgery</t>
+  </si>
+  <si>
+    <t>dof</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="166" formatCode="0.0E+00"/>
+    <numFmt numFmtId="172" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -592,8 +612,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1798,6 +1820,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2336,37 +2367,37 @@
       <c r="C2">
         <v>19</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>66661.733949396366</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>54651.677550418077</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>78671.790348374649</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>24917.92705614349</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>56938.130086701327</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>49873.735400003963</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>77431.585297628073</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>39937.747330113671</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>135224.42582730119</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="2">
         <v>1.2826405065577851</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="2">
         <v>1.393792601950105E-2</v>
       </c>
     </row>
@@ -2380,37 +2411,37 @@
       <c r="C3">
         <v>19</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>69142.112618404513</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>56857.356285190159</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>81426.868951618875</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>25487.86217519956</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>75768.650211735148</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>49237.723806671696</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>83653.689342811675</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>33213.086170539602</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>127037.4901466513</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="2">
         <v>0.54322748333829018</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="2">
         <v>0.2480084803447237</v>
       </c>
     </row>
@@ -2424,37 +2455,37 @@
       <c r="C4">
         <v>19</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-2480.3786690081361</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>-7802.54594682279</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>2841.7886088065179</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>11042.194274829661</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>-454.43140590189432</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>-4949.2820041550949</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>5371.4094400972572</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>-29268.546739700261</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>12253.750369370429</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="2">
         <v>-1.093263132431763</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="2">
         <v>3.5634645491596111E-2</v>
       </c>
     </row>
@@ -2468,37 +2499,37 @@
       <c r="C5">
         <v>11</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>65151.56025544431</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>51405.899193418401</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>78897.221317470219</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>20460.663929223971</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>59907.11501842631</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>51461.536787339501</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>76249.480981365297</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>39937.747330113671</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>108652.64760369041</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="2">
         <v>0.78883043176696921</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="2">
         <v>0.50415102695834058</v>
       </c>
     </row>
@@ -2512,37 +2543,37 @@
       <c r="C6">
         <v>11</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>68223.322694536459</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>51721.75784805174</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>84724.887541021177</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>24562.876321967</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>77780.864287070304</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>47168.423570665982</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>84213.686478664764</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>33213.086170539602</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>112073.0508144085</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="2">
         <v>0.15827549427390561</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="2">
         <v>0.54536645924349281</v>
       </c>
     </row>
@@ -2556,37 +2587,37 @@
       <c r="C7">
         <v>11</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>-3071.7624390921542</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>-11060.570338827671</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>4917.0454606433559</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>11891.48436688768</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>-454.43140590189432</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>-7613.9783360896108</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>5371.4094400972572</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>-29268.546739700261</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>12253.750369370429</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="2">
         <v>-0.92493369088769495</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="2">
         <v>0.32686346556939488</v>
       </c>
     </row>
@@ -2600,37 +2631,37 @@
       <c r="C8">
         <v>8</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>68738.222778580443</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>42432.894659345082</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>95043.550897815803</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>31464.91605491958</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>55076.540107941277</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>49264.243313962506</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>80624.324918891478</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>42695.405278231767</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>135224.42582730119</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="2">
         <v>1.2698046810593959</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="2">
         <v>4.5871257764425501E-2</v>
       </c>
     </row>
@@ -2644,37 +2675,37 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>70405.448763723049</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>46679.203778484611</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>94131.693748961494</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>28379.965586252671</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>66074.46920935587</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>52422.543890696543</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>80367.775662396831</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>36542.6065481435</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>127037.4901466513</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="2">
         <v>0.87174540457038263</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="2">
         <v>0.42710811618418781</v>
       </c>
     </row>
@@ -2688,37 +2719,37 @@
       <c r="C10">
         <v>8</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>-1667.2259851426111</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>-10444.195261706771</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>7109.7432914215506</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>10498.504342994949</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>1140.6258682730329</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>-3993.543757744555</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>4325.2344289741104</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>-24598.246956751191</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>8186.9356806498254</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="2">
         <v>-1.3639450823200769</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="2">
         <v>7.5180915138518503E-2</v>
       </c>
     </row>
@@ -2732,37 +2763,37 @@
       <c r="C11">
         <v>15</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>69904.408953150923</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>54906.913996463467</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>84901.90390983838</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>27081.96974985435</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>59907.11501842631</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>49510.712967860818</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>82436.743967660179</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>39937.747330113671</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>135224.42582730119</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="2">
         <v>0.965355145714486</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="2">
         <v>9.6162526248829427E-2</v>
       </c>
     </row>
@@ -2776,37 +2807,37 @@
       <c r="C12">
         <v>15</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>68194.389044868818</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>52488.001244999323</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>83900.776844738313</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>28362.064498369899</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>55707.032024605069</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>47104.265839818218</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>87077.624448259186</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>33213.086170539602</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>127037.4901466513</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="2">
         <v>0.61302648302567386</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="2">
         <v>0.17784443924573851</v>
       </c>
     </row>
@@ -2820,37 +2851,37 @@
       <c r="C13">
         <v>15</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>1710.01990828212</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>-1755.034511212973</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>5175.0743277772117</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>6257.078214820217</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>2908.7790918297978</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>-1541.1512588847911</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>6633.6985229736711</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>-11807.553461461181</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>12253.750369370429</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="2">
         <v>-0.42393888947224301</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="2">
         <v>0.91698671245046559</v>
       </c>
     </row>
@@ -2864,37 +2895,37 @@
       <c r="C14">
         <v>4</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>54501.702685316719</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>42917.319766867833</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>66086.085603765605</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>7280.1749391439716</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>52192.676692082598</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>50522.069327493962</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>56172.310049905347</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>48577.067545023972</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>65044.389812077687</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="2">
         <v>0.92244792960339217</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="2">
         <v>0.24168878217532749</v>
       </c>
     </row>
@@ -2908,37 +2939,37 @@
       <c r="C15">
         <v>4</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>72696.076019163316</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>55080.366840377414</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>90311.785197949226</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>11070.54604474498</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>76807.132248229696</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>70921.559710545509</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>78581.648556847489</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>56380.288206976591</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>80789.751373217267</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="2">
         <v>-1.0347760465965641</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="2">
         <v>9.7429203444657109E-2</v>
       </c>
     </row>
@@ -2952,37 +2983,37 @@
       <c r="C16">
         <v>4</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>-18194.37333384659</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>-36464.970833980908</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>76.224166287720436</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>11482.10888573376</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>-20171.80425894538</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>-25765.821902488449</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>-12600.355690303521</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>-29268.546739700261</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>-3165.3380777953571</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="2">
         <v>0.45477423161515118</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="2">
         <v>0.73350902826616171</v>
       </c>
     </row>
@@ -3187,7 +3218,7 @@
     <col min="3" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="31.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -3222,7 +3253,7 @@
         <v>141</v>
       </c>
       <c r="H1" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="I1" t="s">
         <v>143</v>
@@ -3259,46 +3290,46 @@
       <c r="B2">
         <v>19</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>66661.733949396366</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>24917.92705614349</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>0.37379656333360539</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>-0.97912785184058648</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>0.34049425859165489</v>
       </c>
       <c r="H2">
         <v>18</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>-2480.3786690081361</v>
       </c>
       <c r="J2" t="s">
         <v>153</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>-7802.54594682279</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>2841.7886088065179</v>
       </c>
       <c r="M2" t="s">
         <v>154</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="2">
         <v>3.5634645491596111E-2</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="2">
         <v>-1.093263132431763</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="2">
         <v>0.79825210571289063</v>
       </c>
       <c r="Q2" t="s">
@@ -3312,46 +3343,46 @@
       <c r="B3">
         <v>19</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>69142.112618404513</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>25487.86217519956</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>0.3686300752172143</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>-0.97912785184058648</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>0.34049425859165489</v>
       </c>
       <c r="H3">
         <v>18</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>-2480.3786690081361</v>
       </c>
       <c r="J3" t="s">
         <v>153</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>-7802.54594682279</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>2841.7886088065179</v>
       </c>
       <c r="M3" t="s">
         <v>154</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="2">
         <v>3.5634645491596111E-2</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="2">
         <v>-1.093263132431763</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="2">
         <v>0.79825210571289063</v>
       </c>
       <c r="Q3" t="s">
@@ -3439,31 +3470,31 @@
       <c r="D2" t="s">
         <v>167</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>-2480.378669008137</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>2533.2531031013618</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-7802.5459468227918</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>2841.7886088065179</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>-0.97912785184058659</v>
       </c>
       <c r="J2">
         <v>18</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="2">
         <v>0.34049425859165477</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="2">
         <v>0.34058344879013008</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="2">
         <v>3.5634645491596111E-2</v>
       </c>
       <c r="N2" t="s">
@@ -3483,31 +3514,31 @@
       <c r="D3" t="s">
         <v>167</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-2369.4942121173831</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>2634.309282619005</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>-7927.4009734178653</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>3188.4125491831001</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>-0.89947457109578821</v>
       </c>
       <c r="J3">
         <v>17</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>0.38096461123965009</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="2">
         <v>0.38601768639485717</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="2">
         <v>3.9045432939055803E-2</v>
       </c>
       <c r="N3" t="s">
@@ -3527,31 +3558,31 @@
       <c r="D4" t="s">
         <v>170</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>1404.5364539495449</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>5268.6185652380072</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>-9711.2770686514159</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>12520.3499765505</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>0.26658533666046402</v>
       </c>
       <c r="J4">
         <v>17</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>0.79299509531799006</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="2">
         <v>0.79724082089869852</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="2">
         <v>3.9045432939055803E-2</v>
       </c>
       <c r="N4" t="s">
@@ -3571,31 +3602,31 @@
       <c r="D5" t="s">
         <v>167</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>-8242.1767127822404</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>2096.2727418537761</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>-12664.92559893269</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>-3819.4278266317879</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>-3.9318245895300441</v>
       </c>
       <c r="J5">
         <v>17</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>1.0748762817945319E-3</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="2">
         <v>1.5904622619350672E-2</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="2">
         <v>0.99526094138010168</v>
       </c>
       <c r="N5" t="s">
@@ -3615,31 +3646,31 @@
       <c r="D6" t="s">
         <v>174</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>19904.393242128721</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>4192.5454837075504</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>11058.89546982781</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>28749.891014429621</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>4.7475676339059936</v>
       </c>
       <c r="J6">
         <v>17</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>1.8642883366514599E-4</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="2">
         <v>3.5989173435683492E-3</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="2">
         <v>0.99526094138010168</v>
       </c>
       <c r="N6" t="s">
@@ -3659,31 +3690,31 @@
       <c r="D7" t="s">
         <v>167</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>-8103.1460678163703</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>2126.9396515042208</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>-12612.056706163979</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>-3594.235429468763</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>-3.8097677393364862</v>
       </c>
       <c r="J7">
         <v>16</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>1.5406549813765059E-3</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="2">
         <v>2.2579182907500661E-2</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="2">
         <v>0.84830261441856725</v>
       </c>
       <c r="N7" t="s">
@@ -3703,31 +3734,31 @@
       <c r="D8" t="s">
         <v>170</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>2780.6128993173088</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>3512.525230374953</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>-4665.6079502029133</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>10226.833748837529</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>0.79162787935917123</v>
       </c>
       <c r="J8">
         <v>16</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>0.44015655331604142</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="2">
         <v>0.48603123818831567</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="2">
         <v>0.84830261441856725</v>
       </c>
       <c r="N8" t="s">
@@ -3747,31 +3778,31 @@
       <c r="D9" t="s">
         <v>174</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>20182.45453206043</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>4253.8793030084407</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>11164.633255365219</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>29200.275808755639</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>4.7444821760191784</v>
       </c>
       <c r="J9">
         <v>16</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>2.1989021618306969E-4</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="2">
         <v>3.3728392543913529E-3</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="2">
         <v>0.84830261441856725</v>
       </c>
       <c r="N9" t="s">
